--- a/PTBR/Lang/PTBR/Dialog/Drama/quru.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/quru.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O quê?</t>
+          <t>Que?</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Hmm-hmm♪</t>
+          <t>Hm-hm♪</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Hã? De onde vem esse canto animado...</t>
+          <t>Hã, de onde vem esse cantarolar animado...</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Hmm-hmm♪</t>
+          <t>Hm-hm♪</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Haha, você parece estar de bom humor, Quruitzia. Que música é essa?</t>
+          <t>Ha, você parece de bom humor, Quruitzia. Que canção é essa?</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(ignora) Hmm-hmm♪ Fantasma～♪</t>
+          <t>(ignora) Hm-hm♪ Fantasma～♪</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(Suspiro)</t>
+          <t>(Engasga)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Hmm-hmm♪</t>
+          <t>Hm-hm♪</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Quruitzia, essa música... foi o Farris quem te ensinou, não foi?</t>
+          <t>Quruitzia, essa canção... foi a Farris que te ensinou, não foi?</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hmm-hmm♪ Azul～♪</t>
+          <t xml:space="preserve"> Hm-hm♪ Azul～♪</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ah, droga, pare...!</t>
+          <t>Ora, caramba, pare...!</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ah, não, quero dizer... Não que seu canto seja ruim nem nada disso. É só que essa música, bem...</t>
+          <t>Ah, não, digo... Não é que seu canto seja ruim nem nada disso. É só que essa canção, bem...</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>...Se essa música se espalhar, pode ser problemático... Sim, essa música é uma mentira. Tulipas azuis fantasmas, vamos, é ridículo, não é? Nem mesmo crianças acreditariam em uma flor assim. Sério, é uma música terrível, haha!</t>
+          <t>...Se essa canção se espalhar, pode dar problema... Sim, essa canção é mentira. Tulipas azuis fantasmas, ora, é ridículo, não é? Até criança não acredita numa flor dessas. Sério, é uma canção péssima, haha!</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Loytel, seu idiota!  </t>
+          <t xml:space="preserve">…Loytel, seu idiota! </t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Será possível... será que ela realmente acredita nas tulipas azuis fantasmas? Não pode ser...</t>
+          <t>Será que... ela acredita mesmo nas tulipas azuis fantasmas? Impossível...</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="L55" s="20" t="inlineStr">
         <is>
-          <t>Hehe, isso faz cócegas, Corgon?</t>
+          <t>Hehe, faz cócegas, Corgon?</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="L61" s="20" t="inlineStr">
         <is>
-          <t>Hehe, faz cócegas, não é, Corgon!</t>
+          <t>Hehe, faz cócegas, né, Corgon!</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hm...?  </t>
+          <t>Hm...?</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sinto alguém... Alguém está vindo dali.  </t>
+          <t>Sinto alguém... Alguém vem vindo de lá.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L67" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem poderia ser, a esta hora?  </t>
+          <t>Quem será, a esta hora?</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Então, este é o lugar...  </t>
+          <t>Então, é aqui...</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="L70" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mokyu...?  </t>
+          <t>Mokyu...?</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L71" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Uma criança dragão e uma garota de olhos amaldiçoados... O que significa isso...?  </t>
+          <t>...Um filhote de dragão e uma garota de mau olhado... Que significado tem isto...?</t>
         </is>
       </c>
     </row>
@@ -1765,9 +1765,8 @@
       </c>
       <c r="L72" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esse homem... Aqueles olhos sinistros sob o capuz... Ele não é humano... Uma existência estranha...  _x000D_
-_x000D_
-Corgon, afaste-se dele. Vá chamar todos.  </t>
+          <t>Este homem... Aqueles olhos sinistros debaixo do capuz... Ele não é humano... Um ser estranho...
+Corgon, fique longe dele. Vá chamar todo mundo.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1798,7 @@
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heh heh heh... Uma existência estranha, é?  </t>
+          <t>Heh heh heh... Um ser estranho, sou?</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1826,7 @@
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que há de tão engraçado?  </t>
+          <t>O que há de tão engraçado?</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1858,7 @@
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não és também uma, ó Quruitzia de olhos amaldiçoados? Não percebes? Um poder antigo habita em ti—uma força destrutiva que traz calamidade.  </t>
+          <t>Não és uma também, Quruitzia de mau olhado? Não te dás conta? Um poder antigo mora dentro de ti: uma força ruinosa que traz calamidade.</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1886,7 @@
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você... Como sabe sobre mim...?  </t>
+          <t>Você... Como sabe de mim...?</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1918,7 @@
       </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ai! Certo, certo, pequenino, já estou indo, então pare de puxar... O quê—Quem... Quem é esse cara?  </t>
+          <t>Ai! Tá bom, tá bom, pequena, já vou, para de puxar... Quê— Quem... Quem é este cara?</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1946,7 @@
       </c>
       <c r="L78" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pessoal!  </t>
+          <t>Todo mundo!</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1978,7 @@
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esse homem...  </t>
+          <t xml:space="preserve">Este homem... </t>
         </is>
       </c>
     </row>
@@ -2024,7 +2023,7 @@
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh... Um dragão lendário, uma bruxa de olhos amaldiçoados e o "Primeiro Alquimista." De fato, este lugar parece saído diretamente de um mito.  </t>
+          <t>Oh... Um dragão lendário, uma bruxa de mau olhado, e o "Primeiro Alquimista". De fato, só este lugar já parece saído de um mito.</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2055,7 @@
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espera, você conhece esse cara, Kettle?  </t>
+          <t>Espera, você conhece esse cara, Kettle?</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2087,7 @@
       </c>
       <c r="L83" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettle... É assim que te chamam agora?  </t>
+          <t>"Kettle"... É esse o seu nome agora?</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2119,7 @@
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Não há motivo para alarme, pessoal. O nome desse homem é Demitas, o Exilado. Provavelmente, ele não pretende nos fazer mal.  </t>
+          <t>...Não há com o que se alarmar, todos. O nome deste homem é Demitas, o Exilado. Ele provavelmente não pretende nos machucar.</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2147,7 @@
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O Exilado...?  </t>
+          <t xml:space="preserve">O Exilado...? </t>
         </is>
       </c>
     </row>
@@ -2180,7 +2179,7 @@
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um ser lamentável que, ao tocar nos tabus do mundo, foi forçado a servir aos deuses para expiar seus pecados. Embora, no caso dele, até o deus a quem servia o tenha abandonado.  </t>
+          <t>Um ser lastimável que, por tocar nos tabus do mundo, é forçado a servir os deuses para expiar seus pecados. Embora, no caso dele, até o deus que servia o tenha abandonado.</t>
         </is>
       </c>
     </row>
@@ -2214,9 +2213,8 @@
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Tu não mudaste. De fato, agora vagueio pela terra, sem rumo, tendo perdido meu propósito e significado.  _x000D_
-_x000D_
-Mas, heh heh... E tu? Encontraste esse significado ou propósito? Parece que ainda sou jovem demais para compreender o sofrimento eterno, "Kettle."  </t>
+          <t>...Tu não mudaste. De fato, agora vago pela terra, sem rumo, tendo perdido sentido e propósito.
+Mas, heh heh... Encontraste-o? Esse sentido ou propósito? Parece que ainda sou jovem demais para entender o sofrimento eterno, "Kettle".</t>
         </is>
       </c>
     </row>
@@ -2250,9 +2248,8 @@
       </c>
       <c r="L88" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sou um alquimista errante, apenas seguindo o vento. Talvez encontre um propósito ao longo do caminho, ou talvez não.  _x000D_
-_x000D_
-Demitas, posso perguntar qual é o motivo de sua vinda a estas terras?  </t>
+          <t>Sou um alquimista andarilho, só vagando ao sabor do vento. Talvez encontre um sentido na jornada, ou talvez não.
+Demitas, posso perguntar o motivo de ter vindo a esta terra?</t>
         </is>
       </c>
     </row>
@@ -2286,9 +2283,8 @@
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Um demônio que espreitava aqui desde os tempos antigos desapareceu. Tephra, creio que se chamava.  _x000D_
-_x000D_
-Apenas parei para ver o que estava acontecendo.  </t>
+          <t>...Um demônio que espreitava aqui desde a antiguidade sumiu. Tephra, acredito que se chamava.
+Apenas passei para ver o que se passava.</t>
         </is>
       </c>
     </row>
@@ -2322,10 +2318,8 @@
       </c>
       <c r="L90" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Não, talvez eu tenha sido atraído pelo fedor repulsivo do destino que impregna esta terra.  _x000D_
-Crianças lastimáveis, tolas e detestáveis, abandonadas pelos deuses, estão prestes a desencadear outro frenesi.  _x000D_
-_x000D_
-Interessante. Ficarei por aqui por um tempo e observarei silenciosamente como as coisas se desenrolam.  </t>
+          <t>...Não, talvez tenha sido atraído pelo fedor do destino que permeia esta terra. Crianças lastimáveis, tolas e detestáveis abandonadas pelos deuses estão para começar outra frenesi.
+Interessante. Ficarei aqui por um tempo e observarei em silêncio como as coisas se desenrolam.</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2609,7 @@
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que aquele homem disse...  </t>
+          <t>O que aquele homem disse...</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2637,7 @@
       </c>
       <c r="L109" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2665,7 @@
       </c>
       <c r="L110" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ugh, isso não sai da minha cabeça.  </t>
+          <t>Ugh, aquilo se gruda na minha cabeça e não sai.</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2714,7 @@
       </c>
       <c r="L112" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O poder adormecido dentro de mim...  </t>
+          <t>O poder dormindo dentro de mim...</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2742,7 @@
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um poder antigo e destrutivo que traz calamidade.  </t>
+          <t>Um poder antigo e ruinoso que traz calamidade.</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2774,7 @@
       </c>
       <c r="L114" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mokyu...  </t>
+          <t>Mokyu...</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2802,7 @@
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desde que conheci Kettle... Não, desde que comecei a viver com Loytel e os outros, tenho tido menos pesadelos. Não precisava pensar sobre quem eu sou.  </t>
+          <t>Desde que conheci Kettle... Não, desde que comecei a viver com Loytel e os outros, tive menos pesadelos. Eu não precisava pensar em quem eu sou.</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2830,7 @@
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mas...  </t>
+          <t>Mas...</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2858,7 @@
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corgon, eu...  </t>
+          <t>Corgon, eu...</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2890,7 @@
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não consegue dormir, garota?  </t>
+          <t>Não consegue dormir, né, garota?</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2918,7 @@
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demitas...  </t>
+          <t>Demitas...</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2950,7 @@
       </c>
       <c r="L120" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O poder que habita teu olho... Parece que ainda não és capaz de usá-lo.  </t>
+          <t>O poder que mora no teu olho... Parece que ainda não podes manejá-lo.</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que quer dizer com "meu olho"...?  </t>
+          <t>Como assim, meu olho...?</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3010,7 @@
       </c>
       <c r="L122" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heh heh heh... Essa luz... Quando a luz vermelha e catastrófica habitar teu olho, o caos tomará o mundo. Garota de olhos amaldiçoados, tu ainda não conheces teu destino. Mas, com o tempo, o momento chegará. Assim como naquele dia.  </t>
+          <t>Heh heh heh... Aquela luz... Quando a luz vermelha e calamitosa morar no teu olho, o caos descerá sobre o mundo. Garota de mau olhado, ainda não conheces o teu destino. Mas, com o tempo, o momento chegará. Igualzinho àquele dia.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3038,7 @@
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Aquele dia?  </t>
+          <t>...Aquele dia?</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3070,7 @@
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não compreendes? Certamente, não esqueceste a tragédia que se abateu sobre tua vila.  </t>
+          <t>Não percebes? Certamente não esqueceste a tragédia que caiu sobre a tua vila.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3098,7 @@
       </c>
       <c r="L125" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minha vila... Como você sabe...? Nunca nos vimos antes.  </t>
+          <t>Minha vila... Como sabe... Nunca nos encontramos antes.</t>
         </is>
       </c>
     </row>
@@ -3140,11 +3134,9 @@
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heh heh heh... É mesmo?  _x000D_
-_x000D_
-Uma maldição assim, nem eu jamais tinha visto. A luz vermelha que habitava teu olho—seria a chama do ódio, ou um brilho extasiado?  _x000D_
-_x000D_
-Em uma única noite, tua vila foi...  </t>
+          <t>Heh heh heh... É mesmo?
+Tal maldição, nem eu tinha visto antes. A luz vermelha que morava no teu olho: era a chama do ódio, ou um fulgor extático?
+Numa única noite, a tua vila...</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3164,7 @@
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pare com isso!  </t>
+          <t>Pare!</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3213,7 @@
       </c>
       <c r="L129" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pare com isso!  </t>
+          <t>Pare!</t>
         </is>
       </c>
     </row>
@@ -3257,11 +3249,9 @@
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Essa voz... Não... Como fui descuidado em tocar no passado...  _x000D_
-_x000D_
-Teu poder... De fato, todos nós temos observado cuidadosamente aquela que herdou o sangue antigo.  _x000D_
-_x000D_
-Garota, pensaste que foi mero acaso que "Kettle" te salvou naquele dia?  </t>
+          <t>...Essa voz... Não... Que descuido meu trazer o passado à tona...
+Teu poder... De fato, todos vimos vigiando com cuidado você, que herda a linhagem antiga.
+Garota, achavas que foi mera coincidência "Kettle" te salvar naquele dia?</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3279,7 @@
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Me deixe em paz. Não quero ouvir mais nada das suas histórias.  </t>
+          <t>Me deixa. Não quero ouvir mais nenhuma das suas histórias.</t>
         </is>
       </c>
     </row>
@@ -3323,9 +3313,8 @@
       </c>
       <c r="L132" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heh heh heh... Tu nada sabes.  _x000D_
-_x000D_
-Aquele homem apenas está usando todos vocês. Salvou tua vida, uniu-te ao dragão—tudo por desejos egoístas dele.  </t>
+          <t>Heh heh heh... Não sabes de nada.
+Aquele homem está apenas usando vocês. Salvar sua vida, reuní-la ao dragão: tudo por desejos egoístas dele.</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3342,7 @@
       </c>
       <c r="L133" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não acredito em você. Tudo o que diz é mentira!  </t>
+          <t>Não acredito em você. Tudo o que você diz é mentira!</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3374,7 @@
       </c>
       <c r="L134" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mokyu!!  </t>
+          <t>Mokyu!!</t>
         </is>
       </c>
     </row>
@@ -3421,11 +3410,9 @@
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh... O dragão responde à tua raiva? É intrigante que um humano consiga se conectar tão profundamente com um dragão. Mesmo assim, este dragão, ainda jovem...  _x000D_
-_x000D_
-Um filho do Dragão de Aço... Uma pedra mágica... Um receptáculo de pedra...  _x000D_
-_x000D_
-Hehehe, entendo, então é assim que as coisas são.  </t>
+          <t xml:space="preserve">Oh... O dragão responde à sua raiva? É intrigante que uma humana consiga se conectar tão fundo a um dragão. Ainda assim, este dragão, embora jovem...
+Um filho do Dragão de Aço... Uma pedra mágica... Um recipiente de pedra...
+Hehehe, entendi, é assim que é. </t>
         </is>
       </c>
     </row>
@@ -3461,11 +3448,9 @@
       </c>
       <c r="L136" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">A noite avança. Antes de partir, direi uma coisa, garota de olhos amaldiçoados.  _x000D_
-_x000D_
-Essa criança dragão é "pequena demais." Por vontade própria, ou talvez por alguma outra força, o crescimento do dragão está sendo suprimido.  _x000D_
-_x000D_
-Infelizmente, nesse ritmo, não viverá por muito tempo.  </t>
+          <t>A noite fica tarde. Antes de partir, direi uma coisa a você, garota de mau olhado.
+Aquele filhote de dragão é "pequeno demais". Por vontade dele, ou talvez por alguma outra força, o crescimento do dragão está sendo suprimido.
+Infelizmente, neste ritmo, ele não viverá muito.</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3478,7 @@
       </c>
       <c r="L137" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corgon... Espere, explique o que quer dizer!  </t>
+          <t xml:space="preserve">Corgon... Espere, explique o que quer dizer! </t>
         </is>
       </c>
     </row>
@@ -3525,7 +3510,7 @@
       </c>
       <c r="L138" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunte a "Kettle." Parece que ele está escondendo muitos segredos de vocês... Heh heh heh...  </t>
+          <t>Pergunte a "Kettle". Aparentemente ele esconde muitos segredos de vocês... Heh heh heh...</t>
         </is>
       </c>
     </row>
